--- a/금자산가계부_API명세서.xlsx
+++ b/금자산가계부_API명세서.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Back\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7517E29-5990-42DF-9450-FA725ADA36DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4317195-1B12-4C90-8218-2C9F36FF4129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{97E61F76-B047-4BD8-8D4F-73B656E8C3D7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="86">
   <si>
     <t>경로</t>
   </si>
@@ -322,14 +322,6 @@
       </rPr>
       <t>응답</t>
     </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>거래 &gt; 삭제</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/trade/delete</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -763,7 +755,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -827,9 +819,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -857,21 +846,42 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -881,40 +891,13 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1251,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4077427E-9E0B-4EF9-B0CD-6BB2CE2C3E48}">
-  <dimension ref="A1:X78"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="35.08203125" customWidth="1"/>
@@ -1273,14 +1256,14 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-      <c r="J1" s="46"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="38"/>
       <c r="K1" s="3" t="s">
         <v>3</v>
       </c>
@@ -1299,13 +1282,13 @@
       <c r="X1" s="4"/>
     </row>
     <row r="2" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1320,16 +1303,16 @@
       <c r="K2" s="13"/>
     </row>
     <row r="3" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="32"/>
-      <c r="C3" s="32"/>
-      <c r="D3" s="31" t="s">
+      <c r="A3" s="31"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="E3" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="33" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="7" t="s">
@@ -1345,7 +1328,7 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A4" s="50"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
@@ -1364,13 +1347,13 @@
       </c>
     </row>
     <row r="5" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1385,16 +1368,16 @@
       <c r="K5" s="13"/>
     </row>
     <row r="6" spans="1:24" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A6" s="49"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="31" t="s">
+      <c r="A6" s="31"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="33" t="s">
         <v>12</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -1410,12 +1393,12 @@
       </c>
     </row>
     <row r="7" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A7" s="49"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
+      <c r="A7" s="31"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="6" t="s">
         <v>19</v>
       </c>
@@ -1429,14 +1412,14 @@
       </c>
     </row>
     <row r="8" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
+      <c r="A8" s="31"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="15" t="s">
@@ -1444,18 +1427,18 @@
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A9" s="50"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="35"/>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
       <c r="G9" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="15" t="s">
@@ -1482,26 +1465,26 @@
       <c r="D12" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="45"/>
-      <c r="I12" s="45"/>
-      <c r="J12" s="46"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="38"/>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A13" s="36" t="s">
+      <c r="A13" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="31" t="s">
+      <c r="B13" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1516,16 +1499,16 @@
       <c r="K13" s="13"/>
     </row>
     <row r="14" spans="1:24" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A14" s="37"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="31" t="s">
+      <c r="A14" s="43"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="31" t="s">
+      <c r="F14" s="33" t="s">
         <v>12</v>
       </c>
       <c r="G14" s="7" t="s">
@@ -1541,12 +1524,12 @@
       </c>
     </row>
     <row r="15" spans="1:24" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="32"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
       <c r="G15" s="7" t="s">
         <v>44</v>
       </c>
@@ -1556,18 +1539,18 @@
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="16" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="17.5" thickBot="1">
-      <c r="A16" s="37"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="34"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
       <c r="G16" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="15" t="s">
@@ -1575,11 +1558,11 @@
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A17" s="38"/>
+      <c r="A17" s="44"/>
       <c r="B17" s="35"/>
       <c r="C17" s="35"/>
       <c r="D17" s="35"/>
@@ -1596,13 +1579,13 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A18" s="36" t="s">
+      <c r="A18" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="33" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="10" t="s">
@@ -1617,20 +1600,20 @@
       <c r="K18" s="13"/>
     </row>
     <row r="19" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A19" s="37"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="40" t="s">
+      <c r="A19" s="43"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="34"/>
+      <c r="D19" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="33" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="15" t="s">
@@ -1638,16 +1621,16 @@
       </c>
       <c r="J19" s="6"/>
       <c r="K19" s="17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A20" s="37"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
       <c r="G20" s="6" t="s">
         <v>24</v>
       </c>
@@ -1661,14 +1644,14 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A21" s="37"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="32"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
       <c r="G21" s="16" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="15" t="s">
@@ -1676,14 +1659,14 @@
       </c>
       <c r="J21" s="6"/>
       <c r="K21" s="17" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A22" s="38"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="35"/>
       <c r="C22" s="35"/>
-      <c r="D22" s="43"/>
+      <c r="D22" s="41"/>
       <c r="E22" s="35"/>
       <c r="F22" s="35"/>
       <c r="G22" s="6" t="s">
@@ -1699,13 +1682,13 @@
       </c>
     </row>
     <row r="23" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A23" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="31" t="s">
+      <c r="A23" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="39" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="10" t="s">
@@ -1720,16 +1703,16 @@
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="1:11" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A24" s="37"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="41"/>
-      <c r="D24" s="40" t="s">
+      <c r="A24" s="43"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="33" t="s">
         <v>35</v>
       </c>
       <c r="G24" s="6" t="s">
@@ -1741,18 +1724,18 @@
       </c>
       <c r="J24" s="6"/>
       <c r="K24" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A25" s="37"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
       <c r="G25" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="15" t="s">
@@ -1760,16 +1743,16 @@
       </c>
       <c r="J25" s="6"/>
       <c r="K25" s="17" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A26" s="37"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="41"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="6" t="s">
         <v>24</v>
       </c>
@@ -1783,14 +1766,14 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A27" s="37"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
       <c r="G27" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="15" t="s">
@@ -1798,14 +1781,14 @@
       </c>
       <c r="J27" s="6"/>
       <c r="K27" s="17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A28" s="47"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="42"/>
-      <c r="D28" s="43"/>
+      <c r="A28" s="45"/>
+      <c r="B28" s="46"/>
+      <c r="C28" s="47"/>
+      <c r="D28" s="41"/>
       <c r="E28" s="35"/>
       <c r="F28" s="35"/>
       <c r="G28" s="16" t="s">
@@ -1817,7 +1800,7 @@
       </c>
       <c r="J28" s="6"/>
       <c r="K28" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="17.5" thickBot="1">
@@ -1836,33 +1819,33 @@
       <c r="D31" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="46"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="38"/>
       <c r="K31" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A32" s="36" t="s">
+      <c r="A32" s="42" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>58</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="31" t="s">
-        <v>5</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>68</v>
       </c>
       <c r="F32" s="12"/>
       <c r="G32" s="12"/>
@@ -1876,35 +1859,35 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A33" s="37"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
       <c r="D33" s="35"/>
-      <c r="E33" s="26" t="s">
-        <v>69</v>
-      </c>
-      <c r="F33" s="27"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="29" t="s">
+      <c r="E33" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="F33" s="26"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="J33" s="30"/>
+      <c r="J33" s="29"/>
       <c r="K33" s="20" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A34" s="37"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="31" t="s">
+      <c r="A34" s="43"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="34"/>
+      <c r="D34" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="E34" s="31" t="s">
+      <c r="E34" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="31" t="s">
+      <c r="F34" s="33" t="s">
         <v>12</v>
       </c>
       <c r="G34" s="7" t="s">
@@ -1916,18 +1899,18 @@
       </c>
       <c r="J34" s="6"/>
       <c r="K34" s="17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A35" s="37"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
+      <c r="A35" s="43"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
       <c r="G35" s="16" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H35" s="6"/>
       <c r="I35" s="15" t="s">
@@ -1939,12 +1922,12 @@
       </c>
     </row>
     <row r="36" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A36" s="37"/>
-      <c r="B36" s="32"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
-      <c r="E36" s="32"/>
-      <c r="F36" s="32"/>
+      <c r="A36" s="43"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="34"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
       <c r="G36" s="6" t="s">
         <v>41</v>
       </c>
@@ -1958,12 +1941,12 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A37" s="37"/>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
-      <c r="E37" s="32"/>
-      <c r="F37" s="32"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="34"/>
+      <c r="C37" s="34"/>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
       <c r="G37" s="6" t="s">
         <v>37</v>
       </c>
@@ -1977,12 +1960,12 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A38" s="37"/>
-      <c r="B38" s="32"/>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="34"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
       <c r="G38" s="6" t="s">
         <v>24</v>
       </c>
@@ -1996,12 +1979,12 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A39" s="37"/>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
       <c r="G39" s="6" t="s">
         <v>44</v>
       </c>
@@ -2015,12 +1998,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A40" s="37"/>
-      <c r="B40" s="32"/>
-      <c r="C40" s="32"/>
-      <c r="D40" s="32"/>
-      <c r="E40" s="32"/>
-      <c r="F40" s="32"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="34"/>
+      <c r="C40" s="34"/>
+      <c r="D40" s="34"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
       <c r="G40" s="6" t="s">
         <v>46</v>
       </c>
@@ -2034,12 +2017,12 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A41" s="37"/>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
       <c r="G41" s="6" t="s">
         <v>48</v>
       </c>
@@ -2053,12 +2036,12 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A42" s="37"/>
-      <c r="B42" s="32"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
+      <c r="A42" s="43"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
       <c r="G42" s="6" t="s">
         <v>50</v>
       </c>
@@ -2072,7 +2055,7 @@
       </c>
     </row>
     <row r="43" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A43" s="38"/>
+      <c r="A43" s="44"/>
       <c r="B43" s="35"/>
       <c r="C43" s="35"/>
       <c r="D43" s="35"/>
@@ -2091,16 +2074,16 @@
       </c>
     </row>
     <row r="44" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="B44" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C44" s="31" t="s">
+      <c r="C44" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D44" s="31" t="s">
+      <c r="D44" s="33" t="s">
         <v>5</v>
       </c>
       <c r="E44" s="11" t="s">
@@ -2118,12 +2101,12 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A45" s="37"/>
-      <c r="B45" s="32"/>
-      <c r="C45" s="32"/>
-      <c r="D45" s="32"/>
+      <c r="A45" s="43"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
       <c r="E45" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" s="12"/>
@@ -2137,12 +2120,12 @@
       </c>
     </row>
     <row r="46" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A46" s="37"/>
-      <c r="B46" s="32"/>
-      <c r="C46" s="32"/>
-      <c r="D46" s="32"/>
+      <c r="A46" s="43"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
       <c r="E46" s="11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F46" s="12"/>
       <c r="G46" s="12"/>
@@ -2156,12 +2139,12 @@
       </c>
     </row>
     <row r="47" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A47" s="37"/>
-      <c r="B47" s="32"/>
-      <c r="C47" s="32"/>
-      <c r="D47" s="32"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
       <c r="E47" s="11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F47" s="12"/>
       <c r="G47" s="12"/>
@@ -2175,10 +2158,10 @@
       </c>
     </row>
     <row r="48" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A48" s="37"/>
-      <c r="B48" s="32"/>
-      <c r="C48" s="32"/>
-      <c r="D48" s="32"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
       <c r="E48" s="11" t="s">
         <v>44</v>
       </c>
@@ -2194,10 +2177,10 @@
       </c>
     </row>
     <row r="49" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A49" s="37"/>
-      <c r="B49" s="32"/>
-      <c r="C49" s="32"/>
-      <c r="D49" s="32"/>
+      <c r="A49" s="43"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
       <c r="E49" s="11" t="s">
         <v>50</v>
       </c>
@@ -2213,7 +2196,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A50" s="38"/>
+      <c r="A50" s="44"/>
       <c r="B50" s="35"/>
       <c r="C50" s="35"/>
       <c r="D50" s="5" t="s">
@@ -2232,16 +2215,16 @@
       <c r="K50" s="17"/>
     </row>
     <row r="51" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A51" s="36" t="s">
+      <c r="A51" s="42" t="s">
+        <v>79</v>
+      </c>
+      <c r="B51" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="B51" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="31" t="s">
+      <c r="C51" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="D51" s="31" t="s">
+      <c r="D51" s="33" t="s">
         <v>5</v>
       </c>
       <c r="E51" s="11" t="s">
@@ -2255,16 +2238,16 @@
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:11" ht="17.5" customHeight="1" thickBot="1">
-      <c r="A52" s="37"/>
-      <c r="B52" s="32"/>
-      <c r="C52" s="32"/>
-      <c r="D52" s="32"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="34"/>
+      <c r="D52" s="34"/>
       <c r="E52" s="11" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F52" s="12"/>
       <c r="G52" s="12"/>
@@ -2278,10 +2261,10 @@
       </c>
     </row>
     <row r="53" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A53" s="37"/>
-      <c r="B53" s="32"/>
-      <c r="C53" s="32"/>
-      <c r="D53" s="32"/>
+      <c r="A53" s="43"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="34"/>
+      <c r="D53" s="34"/>
       <c r="E53" s="11" t="s">
         <v>41</v>
       </c>
@@ -2297,10 +2280,10 @@
       </c>
     </row>
     <row r="54" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A54" s="37"/>
-      <c r="B54" s="32"/>
-      <c r="C54" s="32"/>
-      <c r="D54" s="32"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="34"/>
+      <c r="D54" s="34"/>
       <c r="E54" s="11" t="s">
         <v>44</v>
       </c>
@@ -2316,10 +2299,10 @@
       </c>
     </row>
     <row r="55" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A55" s="37"/>
-      <c r="B55" s="32"/>
-      <c r="C55" s="32"/>
-      <c r="D55" s="32"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="34"/>
+      <c r="D55" s="34"/>
       <c r="E55" s="11" t="s">
         <v>50</v>
       </c>
@@ -2335,7 +2318,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A56" s="38"/>
+      <c r="A56" s="44"/>
       <c r="B56" s="35"/>
       <c r="C56" s="35"/>
       <c r="D56" s="5" t="s">
@@ -2353,90 +2336,76 @@
       <c r="J56" s="6"/>
       <c r="K56" s="17"/>
     </row>
-    <row r="57" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A57" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D57" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
-      <c r="H57" s="12"/>
-      <c r="I57" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" s="13"/>
-      <c r="K57" s="20" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" ht="17.5" thickBot="1">
-      <c r="A58" s="34"/>
-      <c r="B58" s="35"/>
-      <c r="C58" s="35"/>
-      <c r="D58" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F58" s="9"/>
-      <c r="G58" s="6"/>
-      <c r="H58" s="6"/>
-      <c r="I58" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J58" s="6"/>
-      <c r="K58" s="17"/>
-    </row>
-    <row r="62" spans="1:11" ht="36">
+    <row r="60" spans="1:11" ht="36">
+      <c r="K60" s="21"/>
+    </row>
+    <row r="62" spans="1:11">
       <c r="K62" s="22"/>
     </row>
-    <row r="64" spans="1:11">
+    <row r="64" spans="1:11" ht="21">
       <c r="K64" s="23"/>
     </row>
-    <row r="66" spans="11:11" ht="21">
+    <row r="65" spans="11:11">
+      <c r="K65" s="24"/>
+    </row>
+    <row r="66" spans="11:11">
       <c r="K66" s="24"/>
     </row>
     <row r="67" spans="11:11">
-      <c r="K67" s="25"/>
+      <c r="K67" s="24"/>
     </row>
     <row r="68" spans="11:11">
-      <c r="K68" s="25"/>
+      <c r="K68" s="24"/>
     </row>
     <row r="69" spans="11:11">
-      <c r="K69" s="25"/>
+      <c r="K69" s="24"/>
     </row>
     <row r="70" spans="11:11">
-      <c r="K70" s="25"/>
+      <c r="K70" s="24"/>
     </row>
     <row r="71" spans="11:11">
-      <c r="K71" s="25"/>
+      <c r="K71" s="24"/>
     </row>
     <row r="72" spans="11:11">
-      <c r="K72" s="25"/>
-    </row>
-    <row r="73" spans="11:11">
-      <c r="K73" s="25"/>
-    </row>
-    <row r="74" spans="11:11">
-      <c r="K74" s="25"/>
-    </row>
-    <row r="78" spans="11:11">
-      <c r="K78" s="23"/>
+      <c r="K72" s="24"/>
+    </row>
+    <row r="76" spans="11:11">
+      <c r="K76" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="48">
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="D44:D49"/>
+    <mergeCell ref="A44:A50"/>
+    <mergeCell ref="B44:B50"/>
+    <mergeCell ref="C44:C50"/>
+    <mergeCell ref="A51:A56"/>
+    <mergeCell ref="B51:B56"/>
+    <mergeCell ref="C51:C56"/>
+    <mergeCell ref="E34:E43"/>
+    <mergeCell ref="F34:F43"/>
+    <mergeCell ref="A23:A28"/>
+    <mergeCell ref="B23:B28"/>
+    <mergeCell ref="C23:C28"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="F24:F28"/>
+    <mergeCell ref="A32:A43"/>
+    <mergeCell ref="B32:B43"/>
+    <mergeCell ref="C32:C43"/>
+    <mergeCell ref="D34:D43"/>
+    <mergeCell ref="E31:J31"/>
+    <mergeCell ref="A13:A17"/>
+    <mergeCell ref="B13:B17"/>
+    <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D14:D17"/>
+    <mergeCell ref="C18:C22"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="F19:F22"/>
+    <mergeCell ref="D6:D9"/>
+    <mergeCell ref="C5:C9"/>
+    <mergeCell ref="D19:D22"/>
+    <mergeCell ref="B18:B22"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="E19:E22"/>
     <mergeCell ref="E1:J1"/>
@@ -2453,41 +2422,6 @@
     <mergeCell ref="A5:A9"/>
     <mergeCell ref="F6:F9"/>
     <mergeCell ref="E6:E9"/>
-    <mergeCell ref="F19:F22"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="C5:C9"/>
-    <mergeCell ref="D19:D22"/>
-    <mergeCell ref="B18:B22"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="C13:C17"/>
-    <mergeCell ref="D14:D17"/>
-    <mergeCell ref="C18:C22"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="E34:E43"/>
-    <mergeCell ref="F34:F43"/>
-    <mergeCell ref="A23:A28"/>
-    <mergeCell ref="B23:B28"/>
-    <mergeCell ref="C23:C28"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="F24:F28"/>
-    <mergeCell ref="A32:A43"/>
-    <mergeCell ref="B32:B43"/>
-    <mergeCell ref="C32:C43"/>
-    <mergeCell ref="D34:D43"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="D51:D55"/>
-    <mergeCell ref="D44:D49"/>
-    <mergeCell ref="A57:A58"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="C57:C58"/>
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="C44:C50"/>
-    <mergeCell ref="A51:A56"/>
-    <mergeCell ref="B51:B56"/>
-    <mergeCell ref="C51:C56"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
